--- a/src/test/resources/student_registration.xlsx
+++ b/src/test/resources/student_registration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automation\com.ihsm.university.project\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41CDE7C2-3FE2-4DA0-8D57-299074DA6018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560FB7F3-BE3E-475A-84BC-B0A60749236F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="961" firstSheet="23" activeTab="23" xr2:uid="{83E1AD02-E6B5-41C8-98D7-77709091ACEC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="961" firstSheet="40" activeTab="45" xr2:uid="{83E1AD02-E6B5-41C8-98D7-77709091ACEC}"/>
   </bookViews>
   <sheets>
     <sheet name="StStatus" sheetId="34" r:id="rId1"/>
@@ -58,13 +58,14 @@
     <sheet name="EmpProfessionalInfoMilitaryRank" sheetId="54" r:id="rId43"/>
     <sheet name="EmpDocumentDoc" sheetId="55" r:id="rId44"/>
     <sheet name="EmpDocumentPassport" sheetId="56" r:id="rId45"/>
+    <sheet name="ClassSchedule" sheetId="57" r:id="rId46"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="162">
   <si>
     <t>India</t>
   </si>
@@ -523,6 +524,33 @@
   </si>
   <si>
     <t>ICC</t>
+  </si>
+  <si>
+    <t>academicSession</t>
+  </si>
+  <si>
+    <t>subject</t>
+  </si>
+  <si>
+    <t>classType</t>
+  </si>
+  <si>
+    <t>day</t>
+  </si>
+  <si>
+    <t>frequency</t>
+  </si>
+  <si>
+    <t>timeSlot</t>
+  </si>
+  <si>
+    <t>THU</t>
+  </si>
+  <si>
+    <t>1 Class Every Week</t>
+  </si>
+  <si>
+    <t>07:30 - 09:00</t>
   </si>
 </sst>
 </file>
@@ -1075,7 +1103,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1133,12 +1161,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2356,22 +2378,20 @@
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="23"/>
-      <c r="B3" s="23"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
+      <c r="B3" s="14"/>
+      <c r="D3" s="14"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="23"/>
-      <c r="B4" s="23"/>
-      <c r="C4" s="24"/>
-      <c r="D4" s="24"/>
+      <c r="A4" s="14"/>
+      <c r="B4" s="14"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="23"/>
-      <c r="B5" s="23"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
+      <c r="A5" s="14"/>
+      <c r="B5" s="14"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="20"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B6" s="14"/>
@@ -2394,22 +2414,22 @@
       <c r="D9" s="20"/>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="23"/>
-      <c r="B10" s="23"/>
-      <c r="C10" s="24"/>
-      <c r="D10" s="24"/>
+      <c r="A10" s="14"/>
+      <c r="B10" s="14"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="23"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="24"/>
-      <c r="D11" s="24"/>
+      <c r="A11" s="14"/>
+      <c r="B11" s="14"/>
+      <c r="C11" s="20"/>
+      <c r="D11" s="20"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
+      <c r="A12" s="14"/>
+      <c r="B12" s="14"/>
+      <c r="C12" s="20"/>
+      <c r="D12" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3034,6 +3054,97 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0401A89-8E10-4574-9A89-B67F5814C597}">
+  <dimension ref="A1:K2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="4.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1">
+        <v>0</v>
+      </c>
+      <c r="G2" s="2">
+        <v>46055</v>
+      </c>
+      <c r="H2" s="2">
+        <v>46083</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/src/test/resources/student_registration.xlsx
+++ b/src/test/resources/student_registration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automation\com.ihsm.university.project\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{560FB7F3-BE3E-475A-84BC-B0A60749236F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456EA188-71CB-4377-8172-F914D9F6E6C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="961" firstSheet="40" activeTab="45" xr2:uid="{83E1AD02-E6B5-41C8-98D7-77709091ACEC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="961" firstSheet="25" activeTab="26" xr2:uid="{83E1AD02-E6B5-41C8-98D7-77709091ACEC}"/>
   </bookViews>
   <sheets>
     <sheet name="StStatus" sheetId="34" r:id="rId1"/>
@@ -39,33 +39,36 @@
     <sheet name="ExamManageData" sheetId="4" r:id="rId24"/>
     <sheet name="subjectCreditData" sheetId="5" r:id="rId25"/>
     <sheet name="subjectHoursData" sheetId="37" r:id="rId26"/>
-    <sheet name="GroupAssignmentData" sheetId="38" r:id="rId27"/>
-    <sheet name="FacultyGroupDataShow" sheetId="39" r:id="rId28"/>
-    <sheet name="EmpEnrollnmentInformation" sheetId="40" r:id="rId29"/>
-    <sheet name="EmpPersonalInformation" sheetId="41" r:id="rId30"/>
-    <sheet name="EmpGuardianInformation" sheetId="42" r:id="rId31"/>
-    <sheet name="EmpLanguageInformation" sheetId="43" r:id="rId32"/>
-    <sheet name="EmpVaccinationInformation" sheetId="44" r:id="rId33"/>
-    <sheet name="EmpDesignationEmpRights" sheetId="45" r:id="rId34"/>
-    <sheet name="EmpDesignationPosition" sheetId="46" r:id="rId35"/>
-    <sheet name="EmpProfessionalInfoDegreeLevel" sheetId="47" r:id="rId36"/>
-    <sheet name="EmpProfessionalInfoAcademicDeg" sheetId="48" r:id="rId37"/>
-    <sheet name="EmpProfessionalInfoTitle" sheetId="49" r:id="rId38"/>
-    <sheet name="EmpProfessionalInfoDevSciWork" sheetId="50" r:id="rId39"/>
-    <sheet name="EmpProfessionalInfoDevRewards" sheetId="51" r:id="rId40"/>
-    <sheet name="EmpProfessionalInfoDevPatent" sheetId="52" r:id="rId41"/>
-    <sheet name="EmpProfessionalInfoDevAttes" sheetId="53" r:id="rId42"/>
-    <sheet name="EmpProfessionalInfoMilitaryRank" sheetId="54" r:id="rId43"/>
-    <sheet name="EmpDocumentDoc" sheetId="55" r:id="rId44"/>
-    <sheet name="EmpDocumentPassport" sheetId="56" r:id="rId45"/>
-    <sheet name="ClassSchedule" sheetId="57" r:id="rId46"/>
+    <sheet name="GroupAssignmentData2" sheetId="58" r:id="rId27"/>
+    <sheet name="GroupAssignmentData" sheetId="38" r:id="rId28"/>
+    <sheet name="FacultyGroupDataShow" sheetId="39" r:id="rId29"/>
+    <sheet name="EmpEnrollnmentInformation" sheetId="40" r:id="rId30"/>
+    <sheet name="EmpPersonalInformation" sheetId="41" r:id="rId31"/>
+    <sheet name="EmpGuardianInformation" sheetId="42" r:id="rId32"/>
+    <sheet name="EmpLanguageInformation" sheetId="43" r:id="rId33"/>
+    <sheet name="EmpVaccinationInformation" sheetId="44" r:id="rId34"/>
+    <sheet name="EmpDesignationEmpRights" sheetId="45" r:id="rId35"/>
+    <sheet name="EmpDesignationPosition" sheetId="46" r:id="rId36"/>
+    <sheet name="EmpProfessionalInfoDegreeLevel" sheetId="47" r:id="rId37"/>
+    <sheet name="EmpProfessionalInfoAcademicDeg" sheetId="48" r:id="rId38"/>
+    <sheet name="EmpProfessionalInfoTitle" sheetId="49" r:id="rId39"/>
+    <sheet name="EmpProfessionalInfoDevSciWork" sheetId="50" r:id="rId40"/>
+    <sheet name="EmpProfessionalInfoDevRewards" sheetId="51" r:id="rId41"/>
+    <sheet name="EmpProfessionalInfoDevPatent" sheetId="52" r:id="rId42"/>
+    <sheet name="EmpProfessionalInfoDevAttes" sheetId="53" r:id="rId43"/>
+    <sheet name="EmpProfessionalInfoMilitaryRank" sheetId="54" r:id="rId44"/>
+    <sheet name="EmpDocumentDoc" sheetId="55" r:id="rId45"/>
+    <sheet name="EmpDocumentPassport" sheetId="56" r:id="rId46"/>
+    <sheet name="ClassSchedule" sheetId="57" r:id="rId47"/>
+    <sheet name="ClassSchedule2" sheetId="59" r:id="rId48"/>
+    <sheet name="ClassSchedule3" sheetId="60" r:id="rId49"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="226">
   <si>
     <t>India</t>
   </si>
@@ -103,9 +106,6 @@
     <t>male.png</t>
   </si>
   <si>
-    <t>Mukesh Kumar</t>
-  </si>
-  <si>
     <t>No</t>
   </si>
   <si>
@@ -532,9 +532,6 @@
     <t>subject</t>
   </si>
   <si>
-    <t>classType</t>
-  </si>
-  <si>
     <t>day</t>
   </si>
   <si>
@@ -551,6 +548,204 @@
   </si>
   <si>
     <t>07:30 - 09:00</t>
+  </si>
+  <si>
+    <t>subjectValue</t>
+  </si>
+  <si>
+    <t>Russian language</t>
+  </si>
+  <si>
+    <t>subjectName</t>
+  </si>
+  <si>
+    <t>columnType</t>
+  </si>
+  <si>
+    <t>LEC</t>
+  </si>
+  <si>
+    <t>PRA</t>
+  </si>
+  <si>
+    <t>columnName</t>
+  </si>
+  <si>
+    <t>Russian language (Main)</t>
+  </si>
+  <si>
+    <t>teacherName</t>
+  </si>
+  <si>
+    <t>groupNumber</t>
+  </si>
+  <si>
+    <t>Amit</t>
+  </si>
+  <si>
+    <t>Tamta</t>
+  </si>
+  <si>
+    <t>MON, FRI</t>
+  </si>
+  <si>
+    <t>Alternate Week</t>
+  </si>
+  <si>
+    <t>07:30 - 09:00, 10:00 - 11:35, 16:00 - 17:35</t>
+  </si>
+  <si>
+    <t>Anita Kumari</t>
+  </si>
+  <si>
+    <t>Administration corpus, 310</t>
+  </si>
+  <si>
+    <t>room</t>
+  </si>
+  <si>
+    <t>sub</t>
+  </si>
+  <si>
+    <t>AstraZeneca</t>
+  </si>
+  <si>
+    <t>Thank You</t>
+  </si>
+  <si>
+    <t>сертификат Duolingo</t>
+  </si>
+  <si>
+    <t>Father</t>
+  </si>
+  <si>
+    <t>Mohit Kumar</t>
+  </si>
+  <si>
+    <t>Разведен(а) официально (развод зарегистрирован)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MG Road </t>
+  </si>
+  <si>
+    <t>Gurugram</t>
+  </si>
+  <si>
+    <t>рави</t>
+  </si>
+  <si>
+    <t>ravi1@gmail.com</t>
+  </si>
+  <si>
+    <t>Казахстан</t>
+  </si>
+  <si>
+    <t>Part Time</t>
+  </si>
+  <si>
+    <t>Transfer</t>
+  </si>
+  <si>
+    <t>Academic</t>
+  </si>
+  <si>
+    <t>Faculty</t>
+  </si>
+  <si>
+    <t>Experience in IHSM</t>
+  </si>
+  <si>
+    <t>National University</t>
+  </si>
+  <si>
+    <t>Professor</t>
+  </si>
+  <si>
+    <t>Development</t>
+  </si>
+  <si>
+    <t>England</t>
+  </si>
+  <si>
+    <t>Government of India</t>
+  </si>
+  <si>
+    <t>ABCD1234567</t>
+  </si>
+  <si>
+    <t>Manchester</t>
+  </si>
+  <si>
+    <t>Lieutenant General</t>
+  </si>
+  <si>
+    <t>Excellent</t>
+  </si>
+  <si>
+    <t>Not Suitable</t>
+  </si>
+  <si>
+    <t>Ok</t>
+  </si>
+  <si>
+    <t>Appropriate</t>
+  </si>
+  <si>
+    <t>Patent</t>
+  </si>
+  <si>
+    <t>Smart Water Purification System</t>
+  </si>
+  <si>
+    <t>Republican</t>
+  </si>
+  <si>
+    <t>Amit Sharma</t>
+  </si>
+  <si>
+    <t>Bye</t>
+  </si>
+  <si>
+    <t>Passport Back</t>
+  </si>
+  <si>
+    <t>Диплом кандидата медицинских наук</t>
+  </si>
+  <si>
+    <t>Biology</t>
+  </si>
+  <si>
+    <t>Residency</t>
+  </si>
+  <si>
+    <t>Сертификат</t>
+  </si>
+  <si>
+    <t>Btech</t>
+  </si>
+  <si>
+    <t>Computer Science</t>
+  </si>
+  <si>
+    <t>Методические рекомедации</t>
+  </si>
+  <si>
+    <t>Республикалық деңгей</t>
+  </si>
+  <si>
+    <t>https://www.journal.com</t>
+  </si>
+  <si>
+    <t>International Journal of Science</t>
+  </si>
+  <si>
+    <t>A Study on Deep Learning Models</t>
+  </si>
+  <si>
+    <t>Rohan Singh</t>
+  </si>
+  <si>
+    <t>Latin language (Main)</t>
   </si>
 </sst>
 </file>
@@ -1103,7 +1298,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1161,6 +1356,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1551,21 +1750,21 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>90</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>91</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B2" s="2">
         <v>46023</v>
@@ -1574,7 +1773,7 @@
         <v>4554</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -1597,15 +1796,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>118</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B2" s="2">
         <v>46023</v>
@@ -1629,24 +1828,24 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>121</v>
-      </c>
       <c r="C1" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2" s="2">
         <v>46023</v>
@@ -1685,23 +1884,23 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>76</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>77</v>
       </c>
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B2" s="1">
         <v>3</v>
@@ -1739,10 +1938,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>78</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>79</v>
       </c>
       <c r="C1" s="7"/>
     </row>
@@ -1751,7 +1950,7 @@
         <v>46054</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C2" s="1"/>
     </row>
@@ -1776,10 +1975,10 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>80</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>81</v>
       </c>
       <c r="C1" s="7"/>
     </row>
@@ -1810,22 +2009,22 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="11" t="s">
         <v>84</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>85</v>
       </c>
       <c r="D1" s="13"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B2" s="1">
-        <v>0</v>
+        <v>121</v>
       </c>
       <c r="C2" s="12">
         <v>46023</v>
@@ -1867,13 +2066,13 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B1" s="8"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B2" s="9"/>
     </row>
@@ -1893,13 +2092,13 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B1" s="8"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B2" s="1"/>
     </row>
@@ -1942,18 +2141,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>70</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -1981,34 +2180,34 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="7" t="s">
-        <v>96</v>
-      </c>
       <c r="G1" s="7" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="H1" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="I1" s="7" t="s">
-        <v>59</v>
-      </c>
       <c r="J1" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -2016,10 +2215,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>28</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>29</v>
       </c>
       <c r="D2" s="2">
         <v>44927</v>
@@ -2031,7 +2230,7 @@
         <v>46023</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>0</v>
@@ -2040,7 +2239,7 @@
         <v>7</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -2068,51 +2267,51 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="E1" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="7" t="s">
+      <c r="I1" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="J1" s="7" t="s">
         <v>62</v>
       </c>
-      <c r="G1" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>63</v>
-      </c>
       <c r="K1" s="7" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>175</v>
       </c>
       <c r="C2" s="2">
         <v>25569</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E2" s="1">
         <v>91</v>
@@ -2121,16 +2320,16 @@
         <v>454545245</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>0</v>
@@ -2188,49 +2387,49 @@
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="M1" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="N1" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="M1" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="N1" s="7" t="s">
+      <c r="O1" s="7" t="s">
         <v>60</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
@@ -2238,7 +2437,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
@@ -2250,13 +2449,13 @@
         <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>36</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>37</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>6</v>
@@ -2274,7 +2473,7 @@
         <v>9876500000</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>0</v>
@@ -2302,19 +2501,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>64</v>
-      </c>
       <c r="E1" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -2328,7 +2527,7 @@
         <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>0</v>
@@ -2351,21 +2550,21 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>94</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" s="1">
         <v>5</v>
@@ -2439,42 +2638,48 @@
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{14472D50-E132-4C29-8AF0-3B323C0246C9}">
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E1" s="4" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -2484,89 +2689,93 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3A666A9-01D5-4879-9D19-6D21E146C4C7}">
-  <dimension ref="A1:S2"/>
+  <dimension ref="A1:T2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.77734375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.21875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.6640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="18" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.5546875" customWidth="1"/>
+    <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.6640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="20.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="18" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="K1" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="J1" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="K1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="L1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="S1" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -2577,8 +2786,8 @@
       <c r="D2" s="1">
         <v>1</v>
       </c>
-      <c r="E2" s="1">
-        <v>900</v>
+      <c r="E2" s="1" t="s">
+        <v>161</v>
       </c>
       <c r="F2" s="1">
         <v>900</v>
@@ -2596,30 +2805,33 @@
         <v>900</v>
       </c>
       <c r="K2" s="1">
+        <v>900</v>
+      </c>
+      <c r="L2" s="1">
         <v>500</v>
-      </c>
-      <c r="L2" s="1">
-        <v>50</v>
       </c>
       <c r="M2" s="1">
         <v>50</v>
       </c>
       <c r="N2" s="1">
+        <v>50</v>
+      </c>
+      <c r="O2" s="1">
         <v>40</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="P2" s="1">
+      <c r="P2" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q2" s="1">
         <v>100</v>
       </c>
-      <c r="Q2" s="1">
+      <c r="R2" s="1">
         <v>40</v>
       </c>
-      <c r="R2" s="1">
+      <c r="S2" s="1">
         <v>70</v>
       </c>
-      <c r="S2" s="1">
+      <c r="T2" s="1">
         <v>100</v>
       </c>
     </row>
@@ -2629,8 +2841,8 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C03AEA9A-D823-42B1-9E97-76ABAEDD901C}">
-  <dimension ref="A1:F2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABF27CF4-AC6C-4D8A-B9FB-C566E8C73110}">
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
@@ -2638,47 +2850,61 @@
     <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="57" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="57" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>129</v>
-      </c>
       <c r="D1" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>148</v>
-      </c>
-      <c r="F2" s="6" t="s">
-        <v>151</v>
+        <v>147</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>150</v>
       </c>
     </row>
   </sheetData>
@@ -2687,6 +2913,78 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C03AEA9A-D823-42B1-9E97-76ABAEDD901C}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="57" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>150</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66EB2EB8-C53F-4522-AE97-BD9F3ED1075A}">
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2700,30 +2998,30 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>129</v>
-      </c>
       <c r="D1" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B2" s="9">
         <v>1</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D2" s="9">
         <v>1</v>
@@ -2733,15 +3031,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACDF0D32-5438-433D-8833-D1A91F195AB8}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2764,28 +3053,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>96</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>98</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -2793,7 +3082,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" s="2">
         <v>45658</v>
@@ -2808,7 +3097,7 @@
         <v>85</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H2" s="1">
         <v>90</v>
@@ -2820,91 +3109,520 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D1DEF3E-13BC-4703-9CAA-0CF889CDB13F}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACDF0D32-5438-433D-8833-D1A91F195AB8}">
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="1">
+        <v>9813981398</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>189</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1" xr:uid="{C69E2787-18AD-422B-8591-546F0597A7CD}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93DB15A7-844B-48D5-A4B4-A0BD10E38A41}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D1DEF3E-13BC-4703-9CAA-0CF889CDB13F}">
+  <dimension ref="A1:M2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="4.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="4.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="49" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D2" s="1">
+        <v>25678</v>
+      </c>
+      <c r="E2" s="1">
+        <v>456</v>
+      </c>
+      <c r="F2" s="2">
+        <v>36526</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>184</v>
+      </c>
+      <c r="I2" s="2">
+        <v>46023</v>
+      </c>
+      <c r="J2" s="1">
+        <v>91</v>
+      </c>
+      <c r="K2" s="1">
+        <v>9813981398</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB826918-283E-417C-B6A5-DF504979019A}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93DB15A7-844B-48D5-A4B4-A0BD10E38A41}">
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>182</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="C2" s="2">
+        <v>25569</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51D6202F-9484-4378-9BED-A136A413309A}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB826918-283E-417C-B6A5-DF504979019A}">
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="6"/>
+      <c r="B1" s="6"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="23" t="s">
+        <v>181</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2E648ED-2968-4ACF-8A3B-67BC87B690D1}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51D6202F-9484-4378-9BED-A136A413309A}">
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" customWidth="1"/>
+    <col min="3" max="3" width="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="B2" s="1">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1">
+        <v>2456</v>
+      </c>
+      <c r="D2" s="2">
+        <v>46023</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1F57C77-647E-4AF1-A36B-02113D54C335}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2E648ED-2968-4ACF-8A3B-67BC87B690D1}">
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="26.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="B2" s="1">
+        <v>0.25</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D2" s="1">
+        <v>12589</v>
+      </c>
+      <c r="E2" s="2">
+        <v>46023</v>
+      </c>
+      <c r="F2" s="2">
+        <v>46388</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="I2" s="24" t="s">
+        <v>33</v>
+      </c>
+      <c r="J2" s="1">
+        <v>2</v>
+      </c>
+      <c r="K2" s="2">
+        <v>46023</v>
+      </c>
+      <c r="L2" s="1">
+        <v>2589</v>
+      </c>
+      <c r="M2" s="1">
+        <v>200000</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18A0DFCE-FAFB-4FE1-9548-BEA1466284EB}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B1F57C77-647E-4AF1-A36B-02113D54C335}">
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="B2" s="2">
+        <v>46023</v>
+      </c>
+      <c r="C2" s="2">
+        <v>46388</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4687CD21-B589-4674-BD99-9E2C42FEE6D0}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18A0DFCE-FAFB-4FE1-9548-BEA1466284EB}">
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="34.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="24" t="s">
+        <v>213</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>214</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="D2" s="1">
+        <v>9856</v>
+      </c>
+      <c r="E2" s="2">
+        <v>46023</v>
+      </c>
+      <c r="F2" s="2">
+        <v>46388</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet38.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3CFDB46-A359-4B59-8057-6879D2A02E7D}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4687CD21-B589-4674-BD99-9E2C42FEE6D0}">
+  <dimension ref="A1:J2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="5" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>216</v>
+      </c>
+      <c r="C2" s="2">
+        <v>46023</v>
+      </c>
+      <c r="D2" s="2">
+        <v>46388</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="H2" s="1">
+        <v>4561</v>
+      </c>
+      <c r="I2" s="2">
+        <v>46753</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet39.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2971EC2-3993-4D74-96C8-52402878186F}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F3CFDB46-A359-4B59-8057-6879D2A02E7D}">
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="C2" s="1">
+        <v>523</v>
+      </c>
+      <c r="D2" s="2">
+        <v>46023</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -2930,45 +3648,45 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="E1" s="7" t="s">
+      <c r="G1" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="J1" s="7" t="s">
         <v>95</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>88</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>96</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>24</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>25</v>
       </c>
       <c r="D2" s="2">
         <v>45292</v>
@@ -2977,13 +3695,13 @@
         <v>45658</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>26</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="I2" s="22">
         <v>88</v>
@@ -3005,119 +3723,395 @@
 </file>
 
 <file path=xl/worksheets/sheet40.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46508DBD-069B-435D-B2B1-075B894AFAF2}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2971EC2-3993-4D74-96C8-52402878186F}">
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="25.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="33.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="32.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="24" t="s">
+        <v>219</v>
+      </c>
+      <c r="B2" s="2">
+        <v>46023</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>220</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>222</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>223</v>
+      </c>
+      <c r="G2" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="H2" s="24" t="s">
+        <v>180</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{B976A0ED-3B0F-4DF9-B256-B08858C9C19F}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet41.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B431B5FF-0996-4DE2-9685-AFA791F25E8C}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46508DBD-069B-435D-B2B1-075B894AFAF2}">
+  <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="15.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="24" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="2">
+        <v>46023</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>212</v>
+      </c>
+      <c r="D2" s="1">
+        <v>246</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet42.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3A8289A-68C7-4FB1-9AF5-455662321A1A}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B431B5FF-0996-4DE2-9685-AFA791F25E8C}">
+  <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="3.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>208</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D2" s="24" t="s">
+        <v>210</v>
+      </c>
+      <c r="E2" s="1">
+        <v>589</v>
+      </c>
+      <c r="F2" s="2">
+        <v>46023</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95A29BAA-8E00-4A06-9811-FB485C6FEC34}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3A8289A-68C7-4FB1-9AF5-455662321A1A}">
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E2" s="2">
+        <v>46023</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48B06D56-4AE2-4FB3-9A2A-01EE13383843}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95A29BAA-8E00-4A06-9811-FB485C6FEC34}">
+  <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B2" s="1">
+        <v>2598</v>
+      </c>
+      <c r="C2" s="2">
+        <v>46023</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1FB5685-5617-4B13-AEC1-D921D2BFDF5C}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48B06D56-4AE2-4FB3-9A2A-01EE13383843}">
+  <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>180</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1FB5685-5617-4B13-AEC1-D921D2BFDF5C}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+      <c r="H1" s="1"/>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>197</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1256</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>200</v>
+      </c>
+      <c r="F2" s="24" t="s">
+        <v>201</v>
+      </c>
+      <c r="G2" s="2">
+        <v>46023</v>
+      </c>
+      <c r="H2" s="2">
+        <v>46388</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0401A89-8E10-4574-9A89-B67F5814C597}">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="11.88671875" customWidth="1"/>
+    <col min="10" max="11" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="G1" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="I1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="J1" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
-      <c r="C2" s="1">
-        <v>1</v>
+      <c r="C2" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -3125,23 +4119,270 @@
       <c r="E2" s="1">
         <v>1</v>
       </c>
-      <c r="F2" s="1">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
+      <c r="F2" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="I2" s="1">
+        <v>2</v>
+      </c>
+      <c r="J2" s="2">
         <v>46055</v>
       </c>
-      <c r="H2" s="2">
+      <c r="K2" s="2">
         <v>46083</v>
       </c>
+      <c r="L2" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F74FEF2-0771-4577-8825-6B4054426BF5}">
+  <dimension ref="A1:N2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="34.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="I2" s="1">
+        <v>3</v>
+      </c>
+      <c r="J2" s="2">
+        <v>46055</v>
+      </c>
+      <c r="K2" s="2">
+        <v>46083</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9CFC17A-38DE-45EB-B07A-CB8DAD8DD345}">
+  <dimension ref="A1:P2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="34.77734375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="N1" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="O1" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="P1" s="4" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>161</v>
+      </c>
       <c r="I2" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>160</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>161</v>
+        <v>171</v>
+      </c>
+      <c r="J2" s="1">
+        <v>2</v>
+      </c>
+      <c r="K2" s="2">
+        <v>46055</v>
+      </c>
+      <c r="L2" s="2">
+        <v>46083</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>172</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -3161,12 +4402,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
@@ -3188,21 +4429,21 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C1" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1" s="11" t="s">
         <v>94</v>
-      </c>
-      <c r="D1" s="11" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -3235,39 +4476,39 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>95</v>
-      </c>
       <c r="E1" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="G1" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>116</v>
-      </c>
       <c r="H1" s="4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="I1" s="19" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C2" s="2">
         <v>47484</v>
@@ -3282,13 +4523,13 @@
         <v>49310</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>
@@ -3310,24 +4551,24 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>95</v>
-      </c>
       <c r="D1" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>112</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>113</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B2" s="2">
         <v>49310</v>
@@ -3339,7 +4580,7 @@
         <v>51136</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -3360,21 +4601,21 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>110</v>
-      </c>
       <c r="D1" s="7" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>0</v>
@@ -3383,7 +4624,7 @@
         <v>46023</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
@@ -3392,6 +4633,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -3400,7 +4647,7 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C8BB2145AC5254468C792DE10D43AC94" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2e5a2447409261ea00061a7e0347d58b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="facf0261-3046-4379-83e6-4b564f239035" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="60aaf839d7127e9db1ed69495fc40e99" ns3:_="">
     <xsd:import namespace="facf0261-3046-4379-83e6-4b564f239035"/>
@@ -3544,13 +4791,23 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51273304-BDAD-4DD0-B8B1-1249F784DB7A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="facf0261-3046-4379-83e6-4b564f239035"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD24E627-8D77-45E6-A2E8-6D72477AEF2F}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
@@ -3558,7 +4815,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A7BBEB4-EFA4-4BBC-AEC4-BF9096A43876}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3574,20 +4831,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51273304-BDAD-4DD0-B8B1-1249F784DB7A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="facf0261-3046-4379-83e6-4b564f239035"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/src/test/resources/student_registration.xlsx
+++ b/src/test/resources/student_registration.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automation\com.ihsm.university.project\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456EA188-71CB-4377-8172-F914D9F6E6C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92254A5D-AABD-457A-A1C6-1E0E1B8C61B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="961" firstSheet="25" activeTab="26" xr2:uid="{83E1AD02-E6B5-41C8-98D7-77709091ACEC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="961" firstSheet="16" activeTab="18" xr2:uid="{83E1AD02-E6B5-41C8-98D7-77709091ACEC}"/>
   </bookViews>
   <sheets>
     <sheet name="StStatus" sheetId="34" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="389" uniqueCount="226">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="227">
   <si>
     <t>India</t>
   </si>
@@ -118,9 +118,6 @@
     <t>ID12345</t>
   </si>
   <si>
-    <t>Home Country</t>
-  </si>
-  <si>
     <t>OVNP1234</t>
   </si>
   <si>
@@ -166,9 +163,6 @@
     <t xml:space="preserve"> Haryana (HR) </t>
   </si>
   <si>
-    <t>14 Month Single</t>
-  </si>
-  <si>
     <t>CENTRAL / Bachelor / MBBS</t>
   </si>
   <si>
@@ -746,6 +740,15 @@
   </si>
   <si>
     <t>Latin language (Main)</t>
+  </si>
+  <si>
+    <t>visaAddress</t>
+  </si>
+  <si>
+    <t xml:space="preserve">	Russian language (Main)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 11 Months multi </t>
   </si>
 </sst>
 </file>
@@ -1298,7 +1301,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1361,6 +1364,9 @@
     <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1741,30 +1747,29 @@
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.21875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="D1" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B2" s="2">
         <v>46023</v>
@@ -1773,7 +1778,7 @@
         <v>4554</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -1786,8 +1791,8 @@
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.109375" bestFit="1" customWidth="1"/>
@@ -1796,15 +1801,15 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B2" s="2">
         <v>46023</v>
@@ -1828,24 +1833,24 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" s="2">
         <v>46023</v>
@@ -1873,34 +1878,34 @@
     <col min="7" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="14" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>74</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>75</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>76</v>
       </c>
       <c r="E1" s="7"/>
       <c r="F1" s="7"/>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B2" s="1">
         <v>3</v>
@@ -1924,24 +1929,24 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.109375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C1" s="7"/>
     </row>
@@ -1965,20 +1970,20 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C1" s="7"/>
     </row>
@@ -2002,26 +2007,26 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="37.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>82</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="C1" s="11" t="s">
-        <v>84</v>
       </c>
       <c r="D1" s="13"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B2" s="1">
         <v>121</v>
@@ -2043,36 +2048,36 @@
   <cols>
     <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.6640625" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="11" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="9.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="14" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B1" s="8"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B2" s="9"/>
     </row>
@@ -2086,19 +2091,19 @@
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B1" s="8"/>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B2" s="1"/>
     </row>
@@ -2112,7 +2117,7 @@
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
@@ -2141,18 +2146,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -2173,41 +2178,41 @@
     <col min="6" max="6" width="21.109375" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18.109375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B1" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>95</v>
-      </c>
       <c r="G1" s="7" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="H1" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I1" s="7" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J1" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
@@ -2215,10 +2220,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>27</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>28</v>
       </c>
       <c r="D2" s="2">
         <v>44927</v>
@@ -2230,7 +2235,7 @@
         <v>46023</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>0</v>
@@ -2239,7 +2244,7 @@
         <v>7</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
   </sheetData>
@@ -2252,8 +2257,8 @@
   <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.77734375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.88671875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="11.6640625" bestFit="1" customWidth="1"/>
@@ -2267,51 +2272,51 @@
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>64</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="F1" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>67</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="I1" s="7" t="s">
+      <c r="J1" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="K1" s="7" t="s">
         <v>58</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="C2" s="2">
         <v>25569</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E2" s="1">
         <v>91</v>
@@ -2326,10 +2331,10 @@
         <v>0</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>0</v>
@@ -2368,68 +2373,68 @@
   <dimension ref="A1:O2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="23.44140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.88671875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.88671875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="7.44140625" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="11.6640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="19.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.6640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="J1" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="K1" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="L1" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="M1" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="N1" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="O1" s="7" t="s">
         <v>58</v>
-      </c>
-      <c r="M1" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="N1" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="O1" s="7" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="2" spans="1:15" x14ac:dyDescent="0.3">
@@ -2437,7 +2442,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C2" s="1">
         <v>1</v>
@@ -2449,13 +2454,13 @@
         <v>5</v>
       </c>
       <c r="F2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>6</v>
@@ -2473,7 +2478,7 @@
         <v>9876500000</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>0</v>
@@ -2501,19 +2506,19 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>54</v>
-      </c>
       <c r="C1" s="7" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -2527,7 +2532,7 @@
         <v>10</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>0</v>
@@ -2550,21 +2555,21 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>50</v>
-      </c>
       <c r="C1" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B2" s="1">
         <v>5</v>
@@ -2650,36 +2655,36 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>125</v>
-      </c>
       <c r="E1" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -2698,84 +2703,84 @@
     <col min="4" max="4" width="12.5546875" customWidth="1"/>
     <col min="5" max="5" width="15" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="18" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="18.6640625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="20.77734375" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="20.6640625" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="11.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="17" width="18" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="16.5546875" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="13.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="E1" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="F1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>131</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="K1" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="K1" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="L1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="M1" s="4" t="s">
+      <c r="O1" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="N1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>137</v>
       </c>
-      <c r="O1" s="4" t="s">
+      <c r="Q1" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="P1" s="4" t="s">
+      <c r="R1" s="4" t="s">
         <v>139</v>
       </c>
-      <c r="Q1" s="4" t="s">
+      <c r="S1" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="R1" s="4" t="s">
+      <c r="T1" s="4" t="s">
         <v>141</v>
-      </c>
-      <c r="S1" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="T1" s="4" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
@@ -2787,7 +2792,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F2" s="1">
         <v>900</v>
@@ -2820,7 +2825,7 @@
         <v>40</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Q2" s="1">
         <v>100</v>
@@ -2849,134 +2854,134 @@
     <col min="2" max="2" width="5.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="63.6640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" s="1">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>223</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>148</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C03AEA9A-D823-42B1-9E97-76ABAEDD901C}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="27.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.44140625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="57" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>128</v>
-      </c>
       <c r="D1" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>225</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H2" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C03AEA9A-D823-42B1-9E97-76ABAEDD901C}">
-  <dimension ref="A1:H2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="10" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="57" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>163</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" s="1">
-        <v>1</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>147</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>225</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
@@ -2998,30 +3003,30 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>128</v>
-      </c>
       <c r="D1" s="4" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="9" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B2" s="9">
         <v>1</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D2" s="9">
         <v>1</v>
@@ -3053,28 +3058,28 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="F1" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="G1" s="7" t="s">
         <v>95</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="H1" s="7" t="s">
         <v>96</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
@@ -3082,7 +3087,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" s="2">
         <v>45658</v>
@@ -3097,7 +3102,7 @@
         <v>85</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H2" s="1">
         <v>90</v>
@@ -3131,10 +3136,10 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>
@@ -3143,10 +3148,10 @@
         <v>9813981398</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F2" s="24" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
   </sheetData>
@@ -3163,7 +3168,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="4" bestFit="1" customWidth="1"/>
@@ -3194,13 +3199,13 @@
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="D2" s="1">
         <v>25678</v>
@@ -3215,7 +3220,7 @@
         <v>6</v>
       </c>
       <c r="H2" s="24" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="I2" s="2">
         <v>46023</v>
@@ -3227,10 +3232,10 @@
         <v>9813981398</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -3243,7 +3248,7 @@
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="3.33203125" bestFit="1" customWidth="1"/>
@@ -3257,10 +3262,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C2" s="2">
         <v>25569</v>
@@ -3279,7 +3284,7 @@
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="20.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="3.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3289,10 +3294,10 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
   </sheetData>
@@ -3321,7 +3326,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -3333,7 +3338,7 @@
         <v>46023</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -3352,7 +3357,7 @@
     <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.77734375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="26.44140625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -3379,13 +3384,13 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B2" s="1">
         <v>0.25</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D2" s="1">
         <v>12589</v>
@@ -3397,13 +3402,13 @@
         <v>46388</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I2" s="24" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="J2" s="1">
         <v>2</v>
@@ -3418,7 +3423,7 @@
         <v>200000</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -3434,7 +3439,7 @@
     <col min="1" max="1" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3448,7 +3453,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B2" s="2">
         <v>46023</v>
@@ -3457,13 +3462,13 @@
         <v>46388</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -3495,13 +3500,13 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D2" s="1">
         <v>9856</v>
@@ -3513,7 +3518,7 @@
         <v>46388</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -3551,10 +3556,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C2" s="2">
         <v>46023</v>
@@ -3563,13 +3568,13 @@
         <v>46388</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="H2" s="1">
         <v>4561</v>
@@ -3578,7 +3583,7 @@
         <v>46753</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -3591,7 +3596,7 @@
   <dimension ref="A1:E2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.6640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="16" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="4" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -3607,10 +3612,10 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C2" s="1">
         <v>523</v>
@@ -3619,7 +3624,7 @@
         <v>46023</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -3634,59 +3639,59 @@
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.6640625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="14.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.6640625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="D1" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="G1" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="I1" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="J1" s="7" t="s">
         <v>93</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="D2" s="2">
         <v>45292</v>
@@ -3695,13 +3700,13 @@
         <v>45658</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>25</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>26</v>
       </c>
       <c r="I2" s="22">
         <v>88</v>
@@ -3749,28 +3754,28 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="B2" s="2">
         <v>46023</v>
       </c>
       <c r="C2" s="24" t="s">
+        <v>218</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E2" s="24" t="s">
         <v>220</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="F2" s="24" t="s">
         <v>221</v>
       </c>
-      <c r="E2" s="24" t="s">
+      <c r="G2" s="24" t="s">
         <v>222</v>
       </c>
-      <c r="F2" s="24" t="s">
-        <v>223</v>
-      </c>
-      <c r="G2" s="24" t="s">
-        <v>224</v>
-      </c>
       <c r="H2" s="24" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -3808,13 +3813,13 @@
         <v>46023</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D2" s="1">
         <v>246</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -3827,7 +3832,7 @@
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="32.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
@@ -3848,16 +3853,16 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>206</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>207</v>
       </c>
-      <c r="B2" s="24" t="s">
+      <c r="D2" s="24" t="s">
         <v>208</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="D2" s="24" t="s">
-        <v>210</v>
       </c>
       <c r="E2" s="1">
         <v>589</v>
@@ -3866,10 +3871,10 @@
         <v>46023</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -3882,9 +3887,9 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="3.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="3.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
@@ -3900,22 +3905,22 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>203</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>204</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="E2" s="2">
         <v>46023</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -3942,7 +3947,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B2" s="1">
         <v>2598</v>
@@ -3951,7 +3956,7 @@
         <v>46023</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -3977,7 +3982,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
   </sheetData>
@@ -3992,7 +3997,7 @@
   <cols>
     <col min="1" max="1" width="11.5546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11" bestFit="1" customWidth="1"/>
@@ -4011,22 +4016,22 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>195</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>197</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>199</v>
       </c>
       <c r="D2" s="1">
         <v>1256</v>
       </c>
       <c r="E2" s="24" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F2" s="24" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="G2" s="2">
         <v>46023</v>
@@ -4047,71 +4052,72 @@
   <cols>
     <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="11.88671875" customWidth="1"/>
-    <col min="10" max="11" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="10.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="4.5546875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="L1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="M1" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -4120,16 +4126,16 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>164</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>171</v>
+        <v>162</v>
+      </c>
+      <c r="H2" s="25" t="s">
+        <v>159</v>
       </c>
       <c r="I2" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J2" s="2">
         <v>46055</v>
@@ -4138,13 +4144,13 @@
         <v>46083</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>157</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>158</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -4162,68 +4168,68 @@
     <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.88671875" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8.5546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="34.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="34.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E1" s="4" t="s">
+      <c r="M1" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="L1" s="4" t="s">
+      <c r="N1" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -4232,13 +4238,13 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="I2" s="1">
         <v>3</v>
@@ -4250,13 +4256,13 @@
         <v>46083</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -4280,70 +4286,70 @@
     <col min="9" max="10" width="12.109375" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="22.6640625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="34.77734375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="34.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E1" s="4" t="s">
+      <c r="N1" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="O1" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="F1" s="4" t="s">
-        <v>162</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>168</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>169</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="M1" s="4" t="s">
+      <c r="P1" s="4" t="s">
         <v>154</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>177</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B2" s="1">
         <v>1</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
@@ -4352,16 +4358,16 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="J2" s="1">
         <v>2</v>
@@ -4373,16 +4379,16 @@
         <v>46083</v>
       </c>
       <c r="M2" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>174</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>172</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>176</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -4395,14 +4401,13 @@
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.21875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.77734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="19.33203125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" s="15" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.3">
@@ -4429,16 +4434,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D1" s="11" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
@@ -4465,51 +4470,49 @@
   <dimension ref="A1:I2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="7" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="5.77734375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.77734375" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="5.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I1" s="19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>226</v>
+      </c>
+      <c r="B2" s="1"/>
       <c r="C2" s="2">
         <v>47484</v>
       </c>
@@ -4523,13 +4526,13 @@
         <v>49310</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="I2" s="16" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -4539,48 +4542,53 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{183CB891-07B1-419C-9500-43DAB1CEB717}">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>93</v>
+        <v>224</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+        <v>109</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B2" s="2">
+        <v>226</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="2">
         <v>49310</v>
       </c>
-      <c r="C2" s="2">
+      <c r="D2" s="2">
         <v>50406</v>
       </c>
-      <c r="D2" s="2">
+      <c r="E2" s="2">
         <v>51136</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>17</v>
+      <c r="F2" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -4601,22 +4609,20 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="A2" s="1"/>
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -4624,7 +4630,7 @@
         <v>46023</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -4633,21 +4639,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C8BB2145AC5254468C792DE10D43AC94" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2e5a2447409261ea00061a7e0347d58b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="facf0261-3046-4379-83e6-4b564f239035" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="60aaf839d7127e9db1ed69495fc40e99" ns3:_="">
     <xsd:import namespace="facf0261-3046-4379-83e6-4b564f239035"/>
@@ -4791,31 +4782,22 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51273304-BDAD-4DD0-B8B1-1249F784DB7A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="facf0261-3046-4379-83e6-4b564f239035"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD24E627-8D77-45E6-A2E8-6D72477AEF2F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A7BBEB4-EFA4-4BBC-AEC4-BF9096A43876}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4831,4 +4813,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51273304-BDAD-4DD0-B8B1-1249F784DB7A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="facf0261-3046-4379-83e6-4b564f239035"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD24E627-8D77-45E6-A2E8-6D72477AEF2F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/src/test/resources/student_registration.xlsx
+++ b/src/test/resources/student_registration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automation\com.ihsm.university.project\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92254A5D-AABD-457A-A1C6-1E0E1B8C61B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6DA8BF4-4C50-4520-9DDF-63504F6626C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="961" firstSheet="16" activeTab="18" xr2:uid="{83E1AD02-E6B5-41C8-98D7-77709091ACEC}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="961" firstSheet="21" activeTab="26" xr2:uid="{83E1AD02-E6B5-41C8-98D7-77709091ACEC}"/>
   </bookViews>
   <sheets>
     <sheet name="StStatus" sheetId="34" r:id="rId1"/>
@@ -68,7 +68,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="230">
   <si>
     <t>India</t>
   </si>
@@ -739,9 +739,6 @@
     <t>Rohan Singh</t>
   </si>
   <si>
-    <t>Latin language (Main)</t>
-  </si>
-  <si>
     <t>visaAddress</t>
   </si>
   <si>
@@ -749,6 +746,18 @@
   </si>
   <si>
     <t xml:space="preserve"> 11 Months multi </t>
+  </si>
+  <si>
+    <t>expectedMessage</t>
+  </si>
+  <si>
+    <t>Exam Not Saved.</t>
+  </si>
+  <si>
+    <t>testId</t>
+  </si>
+  <si>
+    <t>TC_001</t>
   </si>
 </sst>
 </file>
@@ -758,7 +767,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-14009]dd/mm/yyyy;@"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -917,6 +926,12 @@
       <color rgb="FF3F7F5F"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF2A00FF"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="35">
@@ -1301,7 +1316,7 @@
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1368,6 +1383,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2545,95 +2561,104 @@
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3F61D5DF-4A16-4FA1-BA8E-05C7CD8F33F9}">
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+      <c r="F1" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>229</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="1">
+      <c r="C2" s="1">
         <v>5</v>
-      </c>
-      <c r="C2" s="5">
-        <v>46055</v>
       </c>
       <c r="D2" s="5">
         <v>46055</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" s="5">
+        <v>46055</v>
+      </c>
+      <c r="F2" s="26" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B3" s="14"/>
-      <c r="D3" s="14"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="14"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B4" s="14"/>
-      <c r="C4" s="20"/>
+      <c r="C4" s="14"/>
       <c r="D4" s="20"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="14"/>
-      <c r="B5" s="14"/>
-      <c r="C5" s="20"/>
+      <c r="E4" s="20"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C5" s="14"/>
       <c r="D5" s="20"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B6" s="14"/>
-      <c r="C6" s="20"/>
+      <c r="E5" s="20"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C6" s="14"/>
       <c r="D6" s="20"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B7" s="14"/>
-      <c r="C7" s="20"/>
+      <c r="E6" s="20"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C7" s="14"/>
       <c r="D7" s="20"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="B8" s="14"/>
-      <c r="C8" s="20"/>
+      <c r="E7" s="20"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C8" s="14"/>
       <c r="D8" s="20"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E8" s="20"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B9" s="14"/>
-      <c r="C9" s="20"/>
+      <c r="C9" s="14"/>
       <c r="D9" s="20"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10" s="14"/>
+      <c r="E9" s="20"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B10" s="14"/>
-      <c r="C10" s="20"/>
+      <c r="C10" s="14"/>
       <c r="D10" s="20"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A11" s="14"/>
+      <c r="E10" s="20"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="B11" s="14"/>
-      <c r="C11" s="20"/>
+      <c r="C11" s="14"/>
       <c r="D11" s="20"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A12" s="14"/>
-      <c r="B12" s="14"/>
-      <c r="C12" s="20"/>
-      <c r="D12" s="20"/>
+      <c r="E11" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2854,8 +2879,8 @@
     <col min="2" max="2" width="5.5546875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.44140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="10.6640625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="63.6640625" bestFit="1" customWidth="1"/>
   </cols>
@@ -2903,7 +2928,7 @@
         <v>145</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>163</v>
@@ -2975,7 +3000,7 @@
         <v>145</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>162</v>
@@ -4510,7 +4535,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="2">
@@ -4558,7 +4583,7 @@
         <v>84</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>91</v>
@@ -4575,7 +4600,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="2">
@@ -4639,6 +4664,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C8BB2145AC5254468C792DE10D43AC94" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2e5a2447409261ea00061a7e0347d58b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="facf0261-3046-4379-83e6-4b564f239035" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="60aaf839d7127e9db1ed69495fc40e99" ns3:_="">
     <xsd:import namespace="facf0261-3046-4379-83e6-4b564f239035"/>
@@ -4782,22 +4822,31 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51273304-BDAD-4DD0-B8B1-1249F784DB7A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="facf0261-3046-4379-83e6-4b564f239035"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD24E627-8D77-45E6-A2E8-6D72477AEF2F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A7BBEB4-EFA4-4BBC-AEC4-BF9096A43876}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4813,28 +4862,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51273304-BDAD-4DD0-B8B1-1249F784DB7A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="facf0261-3046-4379-83e6-4b564f239035"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD24E627-8D77-45E6-A2E8-6D72477AEF2F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/src/test/resources/student_registration.xlsx
+++ b/src/test/resources/student_registration.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Automation\com.ihsm.university.project\src\test\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6DA8BF4-4C50-4520-9DDF-63504F6626C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22E7524B-B83B-49F1-B23D-568248B01C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="961" firstSheet="21" activeTab="26" xr2:uid="{83E1AD02-E6B5-41C8-98D7-77709091ACEC}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="961" firstSheet="42" activeTab="47" xr2:uid="{83E1AD02-E6B5-41C8-98D7-77709091ACEC}"/>
   </bookViews>
   <sheets>
     <sheet name="StStatus" sheetId="34" r:id="rId1"/>
@@ -55,20 +55,20 @@
     <sheet name="EmpProfessionalInfoDevSciWork" sheetId="50" r:id="rId40"/>
     <sheet name="EmpProfessionalInfoDevRewards" sheetId="51" r:id="rId41"/>
     <sheet name="EmpProfessionalInfoDevPatent" sheetId="52" r:id="rId42"/>
-    <sheet name="EmpProfessionalInfoDevAttes" sheetId="53" r:id="rId43"/>
-    <sheet name="EmpProfessionalInfoMilitaryRank" sheetId="54" r:id="rId44"/>
-    <sheet name="EmpDocumentDoc" sheetId="55" r:id="rId45"/>
-    <sheet name="EmpDocumentPassport" sheetId="56" r:id="rId46"/>
-    <sheet name="ClassSchedule" sheetId="57" r:id="rId47"/>
-    <sheet name="ClassSchedule2" sheetId="59" r:id="rId48"/>
-    <sheet name="ClassSchedule3" sheetId="60" r:id="rId49"/>
+    <sheet name="ClassSchedule3" sheetId="60" r:id="rId43"/>
+    <sheet name="EmpProfessionalInfoDevAttes" sheetId="53" r:id="rId44"/>
+    <sheet name="EmpProfessionalInfoMilitaryRank" sheetId="54" r:id="rId45"/>
+    <sheet name="EmpDocumentDoc" sheetId="55" r:id="rId46"/>
+    <sheet name="EmpDocumentPassport" sheetId="56" r:id="rId47"/>
+    <sheet name="ClassSchedule" sheetId="57" r:id="rId48"/>
+    <sheet name="ClassSchedule2" sheetId="59" r:id="rId49"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="392" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="384" uniqueCount="230">
   <si>
     <t>India</t>
   </si>
@@ -535,15 +535,9 @@
     <t>timeSlot</t>
   </si>
   <si>
-    <t>THU</t>
-  </si>
-  <si>
     <t>1 Class Every Week</t>
   </si>
   <si>
-    <t>07:30 - 09:00</t>
-  </si>
-  <si>
     <t>subjectValue</t>
   </si>
   <si>
@@ -577,9 +571,6 @@
     <t>Amit</t>
   </si>
   <si>
-    <t>Tamta</t>
-  </si>
-  <si>
     <t>MON, FRI</t>
   </si>
   <si>
@@ -758,6 +749,15 @@
   </si>
   <si>
     <t>TC_001</t>
+  </si>
+  <si>
+    <t>12:00 - 13:35</t>
+  </si>
+  <si>
+    <t>08:00 - 09:35</t>
+  </si>
+  <si>
+    <t>Demo Faculty</t>
   </si>
 </sst>
 </file>
@@ -2326,7 +2326,7 @@
         <v>37</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C2" s="2">
         <v>25569</v>
@@ -2572,7 +2572,7 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>46</v>
@@ -2587,12 +2587,12 @@
         <v>92</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>31</v>
@@ -2607,7 +2607,7 @@
         <v>46055</v>
       </c>
       <c r="F2" s="26" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -2692,7 +2692,7 @@
         <v>123</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -2709,7 +2709,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
   </sheetData>
@@ -2755,7 +2755,7 @@
         <v>127</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>128</v>
@@ -2817,7 +2817,7 @@
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F2" s="1">
         <v>900</v>
@@ -2902,10 +2902,10 @@
         <v>144</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>147</v>
@@ -2928,10 +2928,10 @@
         <v>145</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>148</v>
@@ -2974,10 +2974,10 @@
         <v>144</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>147</v>
@@ -3000,10 +3000,10 @@
         <v>145</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="H2" s="6" t="s">
         <v>148</v>
@@ -3161,7 +3161,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>32</v>
@@ -3173,10 +3173,10 @@
         <v>9813981398</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F2" s="24" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>
@@ -3245,7 +3245,7 @@
         <v>6</v>
       </c>
       <c r="H2" s="24" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="I2" s="2">
         <v>46023</v>
@@ -3257,10 +3257,10 @@
         <v>9813981398</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
     </row>
   </sheetData>
@@ -3287,10 +3287,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C2" s="2">
         <v>25569</v>
@@ -3319,7 +3319,7 @@
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="23" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>41</v>
@@ -3351,7 +3351,7 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="B2" s="1">
         <v>2</v>
@@ -3363,7 +3363,7 @@
         <v>46023</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -3409,13 +3409,13 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="B2" s="1">
         <v>0.25</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D2" s="1">
         <v>12589</v>
@@ -3427,10 +3427,10 @@
         <v>46388</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="I2" s="24" t="s">
         <v>31</v>
@@ -3448,7 +3448,7 @@
         <v>200000</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -3478,7 +3478,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="B2" s="2">
         <v>46023</v>
@@ -3487,13 +3487,13 @@
         <v>46388</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -3525,13 +3525,13 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="D2" s="1">
         <v>9856</v>
@@ -3543,7 +3543,7 @@
         <v>46388</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -3581,10 +3581,10 @@
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="B2" s="24" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C2" s="2">
         <v>46023</v>
@@ -3593,13 +3593,13 @@
         <v>46388</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="H2" s="1">
         <v>4561</v>
@@ -3608,7 +3608,7 @@
         <v>46753</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -3637,10 +3637,10 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C2" s="1">
         <v>523</v>
@@ -3649,7 +3649,7 @@
         <v>46023</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -3779,28 +3779,28 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="24" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B2" s="2">
         <v>46023</v>
       </c>
       <c r="C2" s="24" t="s">
+        <v>215</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="E2" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="F2" s="24" t="s">
         <v>218</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="G2" s="24" t="s">
         <v>219</v>
       </c>
-      <c r="E2" s="24" t="s">
-        <v>220</v>
-      </c>
-      <c r="F2" s="24" t="s">
-        <v>221</v>
-      </c>
-      <c r="G2" s="24" t="s">
-        <v>222</v>
-      </c>
       <c r="H2" s="24" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -3838,13 +3838,13 @@
         <v>46023</v>
       </c>
       <c r="C2" s="24" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="D2" s="1">
         <v>246</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -3878,16 +3878,16 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="B2" s="24" t="s">
+        <v>203</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="D2" s="24" t="s">
         <v>205</v>
-      </c>
-      <c r="B2" s="24" t="s">
-        <v>206</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>207</v>
-      </c>
-      <c r="D2" s="24" t="s">
-        <v>208</v>
       </c>
       <c r="E2" s="1">
         <v>589</v>
@@ -3899,7 +3899,7 @@
         <v>28</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
     </row>
   </sheetData>
@@ -3908,6 +3908,113 @@
 </file>
 
 <file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9CFC17A-38DE-45EB-B07A-CB8DAD8DD345}">
+  <dimension ref="A1:M2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="M1" s="4" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" s="1">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D2" s="1">
+        <v>1</v>
+      </c>
+      <c r="E2" s="1">
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>157</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>168</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>228</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3A8289A-68C7-4FB1-9AF5-455662321A1A}">
   <dimension ref="A1:F2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3930,22 +4037,22 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
+        <v>198</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>199</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>200</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>202</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>203</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>204</v>
       </c>
       <c r="E2" s="2">
         <v>46023</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -3953,7 +4060,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95A29BAA-8E00-4A06-9811-FB485C6FEC34}">
   <dimension ref="A1:D2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -3972,7 +4079,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="B2" s="1">
         <v>2598</v>
@@ -3981,7 +4088,7 @@
         <v>46023</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -3989,7 +4096,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{48B06D56-4AE2-4FB3-9A2A-01EE13383843}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4007,7 +4114,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -4015,7 +4122,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1FB5685-5617-4B13-AEC1-D921D2BFDF5C}">
   <dimension ref="A1:H2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4041,22 +4148,22 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D2" s="1">
         <v>1256</v>
       </c>
       <c r="E2" s="24" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F2" s="24" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="G2" s="2">
         <v>46023</v>
@@ -4070,9 +4177,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0401A89-8E10-4574-9A89-B67F5814C597}">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
@@ -4084,13 +4191,11 @@
     <col min="7" max="7" width="13.109375" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="10.44140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="4.5546875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.6640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
         <v>150</v>
       </c>
@@ -4107,39 +4212,30 @@
         <v>151</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>166</v>
-      </c>
       <c r="I1" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>91</v>
+        <v>153</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="N1" s="4" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="2" spans="1:14" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:11" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>119</v>
       </c>
       <c r="B2" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>31</v>
@@ -4151,31 +4247,22 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H2" s="25" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="I2" s="1">
         <v>1</v>
       </c>
-      <c r="J2" s="2">
-        <v>46055</v>
-      </c>
-      <c r="K2" s="2">
-        <v>46083</v>
-      </c>
-      <c r="L2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>157</v>
+      <c r="K2" s="1" t="s">
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -4183,7 +4270,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F74FEF2-0771-4577-8825-6B4054426BF5}">
   <dimension ref="A1:N2"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -4219,16 +4306,16 @@
         <v>151</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G1" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="H1" s="4" t="s">
-        <v>166</v>
-      </c>
       <c r="I1" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>91</v>
@@ -4263,13 +4350,13 @@
         <v>1</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I2" s="1">
         <v>3</v>
@@ -4281,139 +4368,13 @@
         <v>46083</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9CFC17A-38DE-45EB-B07A-CB8DAD8DD345}">
-  <dimension ref="A1:P2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="23.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.5546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="22.6640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="34.6640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" s="4" t="s">
-        <v>150</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>151</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>160</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>166</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>152</v>
-      </c>
-      <c r="N1" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="O1" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="P1" s="4" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B2" s="1">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D2" s="1">
-        <v>1</v>
-      </c>
-      <c r="E2" s="1">
-        <v>1</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>162</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="I2" s="1" t="s">
         <v>169</v>
-      </c>
-      <c r="J2" s="1">
-        <v>2</v>
-      </c>
-      <c r="K2" s="2">
-        <v>46055</v>
-      </c>
-      <c r="L2" s="2">
-        <v>46083</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="N2" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>171</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -4535,7 +4496,7 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="2">
@@ -4583,7 +4544,7 @@
         <v>84</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>91</v>
@@ -4600,7 +4561,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="2">
@@ -4664,21 +4625,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100C8BB2145AC5254468C792DE10D43AC94" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="2e5a2447409261ea00061a7e0347d58b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="facf0261-3046-4379-83e6-4b564f239035" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="60aaf839d7127e9db1ed69495fc40e99" ns3:_="">
     <xsd:import namespace="facf0261-3046-4379-83e6-4b564f239035"/>
@@ -4822,31 +4768,22 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51273304-BDAD-4DD0-B8B1-1249F784DB7A}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="facf0261-3046-4379-83e6-4b564f239035"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD24E627-8D77-45E6-A2E8-6D72477AEF2F}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A7BBEB4-EFA4-4BBC-AEC4-BF9096A43876}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -4862,4 +4799,28 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{51273304-BDAD-4DD0-B8B1-1249F784DB7A}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="facf0261-3046-4379-83e6-4b564f239035"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD24E627-8D77-45E6-A2E8-6D72477AEF2F}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>